--- a/Logs/AdvanceCustomers.XLSX
+++ b/Logs/AdvanceCustomers.XLSX
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
   <si>
     <t>No</t>
   </si>
@@ -62,13 +62,61 @@
     <t>Fax</t>
   </si>
   <si>
+    <t>Created</t>
+  </si>
+  <si>
+    <t>C00009</t>
+  </si>
+  <si>
+    <t>John Blank</t>
+  </si>
+  <si>
+    <t>This company</t>
+  </si>
+  <si>
+    <t>adminHouse</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>Middle</t>
+  </si>
+  <si>
+    <t>USA</t>
+  </si>
+  <si>
     <t>C00003</t>
   </si>
   <si>
+    <t>John Doe</t>
+  </si>
+  <si>
+    <t>Lv4</t>
+  </si>
+  <si>
+    <t>John House</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0350                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0350384658  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">            </t>
+  </si>
+  <si>
+    <t>C00011</t>
+  </si>
+  <si>
     <t>Wartian Herkku</t>
   </si>
   <si>
-    <t>Pirkko Koskitalo</t>
+    <t>Normie</t>
   </si>
   <si>
     <t>Torikatu 38</t>
@@ -77,13 +125,13 @@
     <t>Oulu</t>
   </si>
   <si>
-    <t>North</t>
+    <t xml:space="preserve">90110               </t>
   </si>
   <si>
     <t>Finland</t>
   </si>
   <si>
-    <t xml:space="preserve">981-443655  </t>
+    <t xml:space="preserve">9810443655  </t>
   </si>
 </sst>
 </file>
@@ -99,15 +147,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -115,12 +169,34 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,80 +477,183 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="3.5703125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.85546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" style="2" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="3">
+        <v>9</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="3">
+        <v>350</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" s="3">
+        <v>3503846958</v>
+      </c>
+      <c r="L2" s="3">
+        <v>904366666</v>
+      </c>
+      <c r="M2" s="3">
+        <v>45629.342326388891</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="B3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G2" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" t="s">
+      <c r="F3" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I2">
-        <v>90110</v>
-      </c>
-      <c r="J2" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="H3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L2" t="s">
-        <v>19</v>
+      <c r="K3" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" s="3">
+        <v>45628.66505787037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
+        <v>11</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M4" s="3">
+        <v>45628.182557870372</v>
       </c>
     </row>
   </sheetData>
